--- a/output/pdf_financials_xlsx/ABI.xlsx
+++ b/output/pdf_financials_xlsx/ABI.xlsx
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.454645</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.720512</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.963974</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.757753</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.578587</v>
       </c>
     </row>
     <row r="35">
@@ -2048,19 +2048,19 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.454645</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.720512</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.963974</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.757753</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.578587</v>
       </c>
     </row>
     <row r="37">
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.537582</v>
+        <v>0.082937</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.7648509999999999</v>
+        <v>0.044339</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.314829</v>
+        <v>0.350855</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>9.664744000000001</v>
+        <v>8.906991</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>17.443965</v>
+        <v>14.865378</v>
       </c>
     </row>
     <row r="49">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/output/pdf_financials_xlsx/ABI.xlsx
+++ b/output/pdf_financials_xlsx/ABI.xlsx
@@ -536,20 +536,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>20.394883</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>7.014494</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1.6e-05</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.26512</v>
@@ -586,20 +580,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
@@ -634,20 +622,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>20.394883</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>7.014494</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1.6e-05</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.26512</v>
@@ -684,20 +666,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0</v>
@@ -732,20 +708,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -780,20 +750,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0</v>
@@ -828,20 +792,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0</v>
@@ -876,20 +834,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="3" t="n">
+        <v>20.394883</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>7.014494</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1.6e-05</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-10.88223</v>
@@ -924,20 +876,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>-0.074461</v>
@@ -972,20 +918,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>-0</v>
@@ -1020,20 +960,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -1068,20 +1002,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>0</v>
@@ -1164,20 +1092,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1364,20 +1286,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -1412,20 +1328,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
@@ -1712,20 +1622,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -3243,10 +3147,10 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>3.72779</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>5.616907</v>
       </c>
     </row>
     <row r="65">
@@ -3495,10 +3399,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.017221</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.018237</v>
       </c>
     </row>
     <row r="71">
@@ -3537,10 +3441,10 @@
         <v>1.520908</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>1.116667</v>
+        <v>1.133888</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.018237</v>
       </c>
     </row>
     <row r="72">
@@ -3705,10 +3609,10 @@
         <v>0.22813</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.532769</v>
+        <v>0.515548</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.360078</v>
+        <v>0.341841</v>
       </c>
     </row>
     <row r="76">
@@ -3915,12 +3819,10 @@
         <v>-0.9926683783598581</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-0.2015658158894079</v>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.2043062085225399</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>-0.030418625132186</v>
       </c>
     </row>
     <row r="81">
@@ -5034,20 +4936,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="3" t="n">
+        <v>3.149891</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>-0.63292</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>7e-06</v>
       </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
@@ -6579,7 +6475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7525,7 +7421,11 @@
           <t>Current portion of lease obligation 11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -9997,18 +9897,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>553,277         (5,113,076)</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -10031,23 +9935,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>0.26512</v>
+      <c r="I57" s="5" t="n">
+        <v>3.149891</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-0.63292</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -10058,17 +9958,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Proceeds from sale of investments                                                               5,962                           -</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Administration 17</t>
+          <t>Acquisition of Pershimex</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -10097,37 +9997,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>3.762272</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>3.657276</v>
+      <c r="J58" s="5" t="n">
+        <v>0.101565</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>actions                                                                                       -          582 000      Share-based compensation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Care and maintenance expenses</t>
+          <t>Impôts différés                              17            (67 363)           (55 385)      Deferred taxes</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -10141,15 +10041,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G59" s="5" t="n">
+        <v>0.000414</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.000794</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -10166,27 +10062,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n">
-        <v>2.702092</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>3.350461</v>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenus d’intérêts                                                (3 522)             (8 832)       Interest income</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses 17</t>
+          <t>fonds de roulement                          4         2 036 831         (1 645 395)      working capital items</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -10200,15 +10100,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G60" s="5" t="n">
+        <v>0.0009810000000000001</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0.00085</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -10225,34 +10121,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n">
-        <v>4.682988</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>8.322676</v>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Exercice d’options                                                                        -           14 000      Options exercised</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Operating loss</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Frais d’émission d’actions                                    (51 719)           (25 800)      Share issuance expenses</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -10263,15 +10159,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G61" s="5" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0.000902</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -10288,34 +10180,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L61" s="5" t="n">
-        <v>-10.88223</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>-15.330413</v>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Finance costs and income</t>
+          <t>d’évaluation                                              (518 675)          (395 187)      assets</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Finance income</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>d’évaluation                                              (518 675)          (395 187)      assets</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -10326,15 +10218,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="5" t="n">
+        <v>0.000773</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0.000441</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -10351,27 +10239,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L62" s="5" t="n">
-        <v>-0.074461</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>-0.101889</v>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Finance costs and income</t>
+          <t>actions                                              582 000                          -      Share-based compensation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Change in fair value of investments 8</t>
+          <t>Impôts différés                              18            (55 385)           (78 364)      Deferred taxes</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -10380,15 +10272,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" s="5" t="n">
+        <v>0.000365</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0009859999999999999</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -10415,24 +10303,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M63" s="5" t="n">
-        <v>0.855118</v>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Finance costs and income</t>
+          <t>Revenus d’intérêts                                                (8 832)           (11 175)       Interest income</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Finance costs (recovery)</t>
+          <t>fonds de roulement                          5          (1 645 395)         (2 594 052)      working capital items</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -10441,15 +10331,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F64" s="5" t="n">
+        <v>0.000687</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.000607</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -10471,27 +10357,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L64" s="5" t="n">
-        <v>0.599372</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>-0.050954</v>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Finance costs and income</t>
+          <t>Exercice d’options                                      14 000                          -      Options exercised</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Loss before income and mining taxes</t>
+          <t>Frais d’émission d’actions                                    (25 800)             (8 573)      Share issuance expenses</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -10500,15 +10390,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" s="5" t="n">
+        <v>0.000587</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.000502</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -10530,27 +10416,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L65" s="5" t="n">
-        <v>-11.407141</v>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v>-16.032688</v>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Finance costs and income</t>
+          <t>d’évaluation                                              (395 187)         (9 914 050)      assets</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Deferred income and mining taxes</t>
+          <t>actifs de prospection et d’évaluation                                                 -       13 211 801       exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -10559,15 +10449,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" s="5" t="n">
+        <v>0.000202</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.000741</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -10589,43 +10475,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L66" s="5" t="n">
-        <v>0.17843</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>-1.611673</v>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Finance costs and income</t>
+          <t>impôts différés                                              (78 364)          (184 391)      Deferred taxes</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>impôts différés                                              (78 364)          (184 391)      Deferred taxes</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>0.0006089999999999999</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.000434</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -10652,39 +10534,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L67" s="5" t="n">
-        <v>-11.585571</v>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v>-14.421015</v>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Finance costs and income</t>
+          <t>Revenus d’intérêts                                          (11 175)             (6 035)       Interest income</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share</t>
+          <t>fonds de roulement                          5         (2 594 052)          (105 870)       capital items</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="5" t="n">
+        <v>9.8e-05</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.00054</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -10711,39 +10593,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L68" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (basic</t>
+          <t>Souscriptions reçues d’avance                                                        -          (280 000)      Prepaid subscriptions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (basic and diluted)</t>
+          <t>Frais d’émission d’actions                                        (8 573)           (88 334)      Share issuance expenses</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>0.000131</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.0009970000000000001</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -10770,39 +10652,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L69" s="5" t="n">
-        <v>492.313234</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>793.947286</v>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SHARE CAPITAL      WARRANTS         DEBENTURE         SURPLUS           DEFICIT          TOTAL</t>
+          <t>d’évaluation                                                 (9 914 050)       (14 889 285)      assets</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BALANCE AS AT JUNE 30, 2024 57,551,585 2,623,249 – 7,650,641</t>
+          <t>actifs de prospection et d’évaluation                     13 211 801       13 485 248       exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="5" t="n">
+        <v>0.000147</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.000494</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -10829,11 +10711,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L70" s="5" t="n">
-        <v>-6.284136</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>-74.109611</v>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -10842,17 +10728,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>EQUITY FINANCING</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Issuance of units (note 15) 8,018,146 3,097,746 – –</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Revenues</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -10889,7 +10775,7 @@
         </is>
       </c>
       <c r="L71" s="5" t="n">
-        <v>11.115892</v>
+        <v>0.26512</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -10905,12 +10791,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EQUITY FINANCING</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Issuance of flow-through shares (note 15) 4,687,748 – – –</t>
+          <t>Administration 17</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -10950,12 +10836,10 @@
         </is>
       </c>
       <c r="L72" s="5" t="n">
-        <v>4.687748</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.762272</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>3.657276</v>
       </c>
     </row>
     <row r="73">
@@ -10966,12 +10850,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Issuance of shares to account payable settlement</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>(note 15) 364,732 135,268 – –</t>
+          <t>Care and maintenance expenses</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -11011,12 +10895,10 @@
         </is>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.702092</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>3.350461</v>
       </c>
     </row>
     <row r="74">
@@ -11027,12 +10909,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Issuance of shares to account payable settlement</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Issuance of shares as advance on contracts (note 15) 2,409,114 890,886 – –</t>
+          <t>Exploration and evaluation expenses 17</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -11072,12 +10954,10 @@
         </is>
       </c>
       <c r="L74" s="5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.682988</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>8.322676</v>
       </c>
     </row>
     <row r="75">
@@ -11088,15 +10968,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Issuance of shares to account payable settlement</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Exercised warrants (note 15) 648,020 (148,020) – –</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Operating loss</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -11133,12 +11017,10 @@
         </is>
       </c>
       <c r="L75" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.88223</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>-15.330413</v>
       </c>
     </row>
     <row r="76">
@@ -11149,15 +11031,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Issuance of shares to account payable settlement</t>
+          <t>Finance costs and income</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Expired warrants – (368,557) – 368,557</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -11193,15 +11079,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L76" s="5" t="n">
+        <v>-0.074461</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>-0.101889</v>
       </c>
     </row>
     <row r="77">
@@ -11212,12 +11094,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Issuance of shares to account payable settlement</t>
+          <t>Finance costs and income</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Share issuance costs (note 15) 91,051 – – 115,383</t>
+          <t>Change in fair value of investments 8</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -11256,11 +11138,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L77" s="5" t="n">
-        <v>-0.744785</v>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-0.951219</v>
+        <v>0.855118</v>
       </c>
     </row>
     <row r="78">
@@ -11271,12 +11155,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Issuance of shares to account payable settlement</t>
+          <t>Finance costs and income</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CONVERTIBLE DEBENTURE (note 13) – – 585,844 –</t>
+          <t>Finance costs (recovery)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -11316,12 +11200,10 @@
         </is>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0.585844</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.599372</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>-0.050954</v>
       </c>
     </row>
     <row r="79">
@@ -11332,12 +11214,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Granted to employees, officers, directors, consultants</t>
+          <t>Finance costs and income</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Granted to employees, officers, directors, consultants or I.R. representatives (note 16) – – – 160,918</t>
+          <t>Loss before income and mining taxes</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -11377,12 +11259,10 @@
         </is>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.160918</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-11.407141</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>-16.032688</v>
       </c>
     </row>
     <row r="80">
@@ -11393,19 +11273,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Granted to employees, officers, directors, consultants</t>
+          <t>Finance costs and income</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NET LOSS FOR THE PERIOD – – – –</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deferred income and mining taxes</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -11442,10 +11318,10 @@
         </is>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-14.421015</v>
+        <v>0.17843</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-14.421015</v>
+        <v>-1.611673</v>
       </c>
     </row>
     <row r="81">
@@ -11456,15 +11332,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Granted to employees, officers, directors, consultants</t>
+          <t>Finance costs and income</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BALANCE AS AT JUNE 30, 2025 73,770,396 6,230,572 585,844 8,295,499</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -11501,10 +11381,10 @@
         </is>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.599534</v>
+        <v>-11.585571</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-89.48184500000001</v>
+        <v>-14.421015</v>
       </c>
     </row>
     <row r="82">
@@ -11515,12 +11395,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SHARE CAPITAL        WARRANTS            SURPLUS               DEFICIT             TOTAL</t>
+          <t>Finance costs and income</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BALANCE AS AT JUNE 30, 2023 52,464,386 621,918 7,374,384</t>
+          <t>Basic and diluted net loss per share</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -11560,10 +11440,10 @@
         </is>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-1.867936</v>
+        <v>-2e-08</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>-62.328624</v>
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="83">
@@ -11574,12 +11454,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EQUITY FINANCING</t>
+          <t>Weighted average number of shares outstanding (basic</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Issuance of units (note 15) 5,023,704 1,978,166 –</t>
+          <t>Weighted average number of shares outstanding (basic and diluted)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -11619,12 +11499,10 @@
         </is>
       </c>
       <c r="L83" s="5" t="n">
-        <v>7.00187</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>492.313234</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>793.947286</v>
       </c>
     </row>
     <row r="84">
@@ -11635,12 +11513,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EQUITY FINANCING</t>
+          <t>SHARE CAPITAL      WARRANTS         DEBENTURE         SURPLUS           DEFICIT          TOTAL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Settlement of royalty payable 63,495 23,165 –</t>
+          <t>BALANCE AS AT JUNE 30, 2024 57,551,585 2,623,249 – 7,650,641</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -11680,12 +11558,10 @@
         </is>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0.08666</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.284136</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>-74.109611</v>
       </c>
     </row>
     <row r="85">
@@ -11701,7 +11577,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Share issuance costs (note 15) – – 900</t>
+          <t>Issuance of units (note 15) 8,018,146 3,097,746 – –</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -11741,10 +11617,12 @@
         </is>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.194516</v>
-      </c>
-      <c r="M85" s="5" t="n">
-        <v>-0.195416</v>
+        <v>11.115892</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -11755,12 +11633,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Granted to employees, officers, directors, consultants</t>
+          <t>EQUITY FINANCING</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Granted to employees, officers, directors, consultants or I.R. representatives – – 275,357</t>
+          <t>Issuance of flow-through shares (note 15) 4,687,748 – – –</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -11800,7 +11678,7 @@
         </is>
       </c>
       <c r="L86" s="5" t="n">
-        <v>0.275357</v>
+        <v>4.687748</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -11816,19 +11694,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Granted to employees, officers, directors, consultants</t>
+          <t>Issuance of shares to account payable settlement</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NET LOSS FOR THE PERIOD – – –</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>(note 15) 364,732 135,268 – –</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -11865,10 +11739,12 @@
         </is>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-11.585571</v>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v>-11.585571</v>
+        <v>0.5</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -11879,12 +11755,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Granted to employees, officers, directors, consultants</t>
+          <t>Issuance of shares to account payable settlement</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BALANCE AS AT JUNE 30, 2024 57,551,585 2,623,249 7,650,641</t>
+          <t>Issuance of shares as advance on contracts (note 15) 2,409,114 890,886 – –</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -11924,10 +11800,12 @@
         </is>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-6.284136</v>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v>-74.109611</v>
+        <v>3.3</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -11938,19 +11816,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Issuance of shares to account payable settlement</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exercised warrants (note 15) 648,020 (148,020) – –</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -11987,10 +11861,12 @@
         </is>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-11.585571</v>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v>-14.421015</v>
+        <v>0.5</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -12001,12 +11877,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Non cash adjustments for</t>
+          <t>Issuance of shares to account payable settlement</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Change in fair value of investments 8</t>
+          <t>Expired warrants – (368,557) – 368,557</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -12050,8 +11926,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M90" s="5" t="n">
-        <v>0.855118</v>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -12062,19 +11940,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Non cash adjustments for</t>
+          <t>Issuance of shares to account payable settlement</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Amortization 9</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Share issuance costs (note 15) 91,051 – – 115,383</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -12111,10 +11985,10 @@
         </is>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.165854</v>
+        <v>-0.744785</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0.192431</v>
+        <v>-0.951219</v>
       </c>
     </row>
     <row r="92">
@@ -12125,12 +11999,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Non cash adjustments for</t>
+          <t>Issuance of shares to account payable settlement</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sale of a property 17</t>
+          <t>CONVERTIBLE DEBENTURE (note 13) – – 585,844 –</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -12169,13 +12043,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v>-1.5</v>
+      <c r="L92" s="5" t="n">
+        <v>0.585844</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -12186,12 +12060,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Non cash adjustments for</t>
+          <t>Granted to employees, officers, directors, consultants</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Deferred income and mining taxes</t>
+          <t>Granted to employees, officers, directors, consultants or I.R. representatives (note 16) – – – 160,918</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -12231,10 +12105,12 @@
         </is>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.170712</v>
-      </c>
-      <c r="M93" s="5" t="n">
-        <v>-1.561389</v>
+        <v>0.160918</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -12245,15 +12121,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Adjustment to provision for restoration of impaired</t>
+          <t>Granted to employees, officers, directors, consultants</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Adjustment to provision for restoration of impaired mining assets</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>NET LOSS FOR THE PERIOD – – – –</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -12290,12 +12170,10 @@
         </is>
       </c>
       <c r="L94" s="5" t="n">
-        <v>0.130398</v>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-14.421015</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>-14.421015</v>
       </c>
     </row>
     <row r="95">
@@ -12306,12 +12184,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Adjustment to provision for restoration of impaired</t>
+          <t>Granted to employees, officers, directors, consultants</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Accretion expense 14</t>
+          <t>BALANCE AS AT JUNE 30, 2025 73,770,396 6,230,572 585,844 8,295,499</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -12351,10 +12229,10 @@
         </is>
       </c>
       <c r="L95" s="5" t="n">
-        <v>0.437746</v>
+        <v>-0.599534</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>0.353117</v>
+        <v>-89.48184500000001</v>
       </c>
     </row>
     <row r="96">
@@ -12365,12 +12243,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Adjustment to provision for restoration of impaired</t>
+          <t>SHARE CAPITAL        WARRANTS            SURPLUS               DEFICIT             TOTAL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Interests on lease obligation 11</t>
+          <t>BALANCE AS AT JUNE 30, 2023 52,464,386 621,918 7,374,384</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -12410,10 +12288,10 @@
         </is>
       </c>
       <c r="L96" s="5" t="n">
-        <v>0.000901</v>
+        <v>-1.867936</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>0.002295</v>
+        <v>-62.328624</v>
       </c>
     </row>
     <row r="97">
@@ -12424,12 +12302,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Adjustment to provision for restoration of impaired</t>
+          <t>EQUITY FINANCING</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Stock-based compensation 16</t>
+          <t>Issuance of units (note 15) 5,023,704 1,978,166 –</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -12469,10 +12347,12 @@
         </is>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0.275357</v>
-      </c>
-      <c r="M97" s="5" t="n">
-        <v>0.160918</v>
+        <v>7.00187</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -12483,12 +12363,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Adjustment to provision for restoration of impaired</t>
+          <t>EQUITY FINANCING</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Change in working capital items 5</t>
+          <t>Settlement of royalty payable 63,495 23,165 –</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -12528,10 +12408,12 @@
         </is>
       </c>
       <c r="L98" s="5" t="n">
-        <v>0.589079</v>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v>-1.613823</v>
+        <v>0.08666</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -12542,12 +12424,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Adjustment to provision for restoration of impaired</t>
+          <t>EQUITY FINANCING</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Adjustment to provision for restoration of impaired total</t>
+          <t>Share issuance costs (note 15) – – 900</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -12587,10 +12469,10 @@
         </is>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-10.156948</v>
+        <v>-0.194516</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>-17.532348</v>
+        <v>-0.195416</v>
       </c>
     </row>
     <row r="100">
@@ -12601,12 +12483,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Granted to employees, officers, directors, consultants</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Repayment of lease obligation 11</t>
+          <t>Granted to employees, officers, directors, consultants or I.R. representatives – – 275,357</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -12646,10 +12528,12 @@
         </is>
       </c>
       <c r="L100" s="5" t="n">
-        <v>-0.006003</v>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v>-0.019521</v>
+        <v>0.275357</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -12660,15 +12544,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Granted to employees, officers, directors, consultants</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Repayment of long-term debt 12</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>NET LOSS FOR THE PERIOD – – –</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -12705,10 +12593,10 @@
         </is>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.587574</v>
+        <v>-11.585571</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>-1.266667</v>
+        <v>-11.585571</v>
       </c>
     </row>
     <row r="102">
@@ -12719,12 +12607,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Granted to employees, officers, directors, consultants</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Convertible debenture 13</t>
+          <t>BALANCE AS AT JUNE 30, 2024 57,551,585 2,623,249 7,650,641</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -12763,13 +12651,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L102" s="5" t="n">
+        <v>-6.284136</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>3</v>
+        <v>-74.109611</v>
       </c>
     </row>
     <row r="103">
@@ -12780,15 +12666,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Issuance of shares and units 15</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -12825,10 +12715,10 @@
         </is>
       </c>
       <c r="L103" s="5" t="n">
-        <v>7.00187</v>
+        <v>-11.585571</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>18.043056</v>
+        <v>-14.421015</v>
       </c>
     </row>
     <row r="104">
@@ -12839,12 +12729,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non cash adjustments for</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Shares and units issuance costs</t>
+          <t>Change in fair value of investments 8</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -12883,11 +12773,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L104" s="5" t="n">
-        <v>-0.099083</v>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="5" t="n">
-        <v>-0.636454</v>
+        <v>0.855118</v>
       </c>
     </row>
     <row r="105">
@@ -12898,15 +12790,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non cash adjustments for</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Financing activities total</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Amortization 9</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -12943,10 +12839,10 @@
         </is>
       </c>
       <c r="L105" s="5" t="n">
-        <v>6.30921</v>
+        <v>0.165854</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>19.120414</v>
+        <v>0.192431</v>
       </c>
     </row>
     <row r="106">
@@ -12957,12 +12853,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non cash adjustments for</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Disposal of investments 8</t>
+          <t>Sale of a property 17</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -13007,7 +12903,7 @@
         </is>
       </c>
       <c r="M106" s="5" t="n">
-        <v>0.644882</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="107">
@@ -13018,12 +12914,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on</t>
+          <t>Non cash adjustments for</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on mining rights</t>
+          <t>Deferred income and mining taxes</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -13063,12 +12959,10 @@
         </is>
       </c>
       <c r="L107" s="5" t="n">
-        <v>0.224847</v>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.170712</v>
+      </c>
+      <c r="M107" s="5" t="n">
+        <v>-1.561389</v>
       </c>
     </row>
     <row r="108">
@@ -13079,12 +12973,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on</t>
+          <t>Adjustment to provision for restoration of impaired</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Supplier deposit</t>
+          <t>Adjustment to provision for restoration of impaired mining assets</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -13124,7 +13018,7 @@
         </is>
       </c>
       <c r="L108" s="5" t="n">
-        <v>-0.211683</v>
+        <v>0.130398</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -13140,12 +13034,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on</t>
+          <t>Adjustment to provision for restoration of impaired</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Deposit for restoration 14</t>
+          <t>Accretion expense 14</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -13185,12 +13079,10 @@
         </is>
       </c>
       <c r="L109" s="5" t="n">
-        <v>3.867786</v>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.437746</v>
+      </c>
+      <c r="M109" s="5" t="n">
+        <v>0.353117</v>
       </c>
     </row>
     <row r="110">
@@ -13201,12 +13093,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on</t>
+          <t>Adjustment to provision for restoration of impaired</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Acquisition of property, plant and equipment 9</t>
+          <t>Interests on lease obligation 11</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -13246,10 +13138,10 @@
         </is>
       </c>
       <c r="L110" s="5" t="n">
-        <v>-0.239433</v>
+        <v>0.000901</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.412114</v>
+        <v>0.002295</v>
       </c>
     </row>
     <row r="111">
@@ -13260,12 +13152,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on</t>
+          <t>Adjustment to provision for restoration of impaired</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on total</t>
+          <t>Stock-based compensation 16</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -13305,10 +13197,10 @@
         </is>
       </c>
       <c r="L111" s="5" t="n">
-        <v>3.641517</v>
+        <v>0.275357</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>0.232768</v>
+        <v>0.160918</v>
       </c>
     </row>
     <row r="112">
@@ -13319,12 +13211,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on</t>
+          <t>Adjustment to provision for restoration of impaired</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Change in working capital items 5</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -13364,10 +13256,10 @@
         </is>
       </c>
       <c r="L112" s="5" t="n">
-        <v>-0.206221</v>
+        <v>0.589079</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>1.820834</v>
+        <v>-1.613823</v>
       </c>
     </row>
     <row r="113">
@@ -13378,12 +13270,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on</t>
+          <t>Adjustment to provision for restoration of impaired</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Adjustment to provision for restoration of impaired total</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -13423,10 +13315,10 @@
         </is>
       </c>
       <c r="L113" s="5" t="n">
-        <v>0.963974</v>
+        <v>-10.156948</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>0.757753</v>
+        <v>-17.532348</v>
       </c>
     </row>
     <row r="114">
@@ -13437,12 +13329,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Refundable tax credit resources and refundable credit on</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Repayment of lease obligation 11</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -13482,10 +13374,10 @@
         </is>
       </c>
       <c r="L114" s="5" t="n">
-        <v>0.757753</v>
+        <v>-0.006003</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>2.578587</v>
+        <v>-0.019521</v>
       </c>
     </row>
     <row r="115">
@@ -13496,12 +13388,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rémunération et paiements</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>fondés sur des actions                                                  -           582 000      Share-based compensation</t>
+          <t>Repayment of long-term debt 12</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -13515,11 +13407,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" s="5" t="n">
-        <v>0.000853</v>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>0.000508</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -13536,15 +13432,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L115" s="5" t="n">
+        <v>-0.587574</v>
+      </c>
+      <c r="M115" s="5" t="n">
+        <v>-1.266667</v>
       </c>
     </row>
     <row r="116">
@@ -13555,12 +13447,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Rémunération et paiements</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>fondés sur des actions                        582 000                            -      Share-based compensation</t>
+          <t>Convertible debenture 13</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -13569,11 +13461,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F116" s="5" t="n">
-        <v>6.7e-05</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>0.000552</v>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -13600,10 +13496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M116" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -13614,52 +13508,1480 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Issuance of shares and units 15</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>7.00187</v>
+      </c>
+      <c r="M117" s="5" t="n">
+        <v>18.043056</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Shares and units issuance costs</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>-0.099083</v>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>-0.636454</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Financing activities total</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>6.30921</v>
+      </c>
+      <c r="M119" s="5" t="n">
+        <v>19.120414</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Disposal of investments 8</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="n">
+        <v>0.644882</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on mining rights</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>0.224847</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Supplier deposit</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>-0.211683</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Deposit for restoration 14</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>3.867786</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Acquisition of property, plant and equipment 9</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>-0.239433</v>
+      </c>
+      <c r="M124" s="5" t="n">
+        <v>-0.412114</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on total</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>3.641517</v>
+      </c>
+      <c r="M125" s="5" t="n">
+        <v>0.232768</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>-0.206221</v>
+      </c>
+      <c r="M126" s="5" t="n">
+        <v>1.820834</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>0.963974</v>
+      </c>
+      <c r="M127" s="5" t="n">
+        <v>0.757753</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Refundable tax credit resources and refundable credit on</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>0.757753</v>
+      </c>
+      <c r="M128" s="5" t="n">
+        <v>2.578587</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Revenues</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>20.394883</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>7.014494</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>1.6e-05</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ADMINISTRATION</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>15.978882</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>2.128357</v>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>1.7e-05</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CARE AND MAINTENANCE                                                           4,046,339                         -</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>EXPLORATION AND EVALUATION 17 -</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>3.077692</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>1.644117</v>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>2.4e-05</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EARNINGS BEFORE INCOME AND MINING TAXES                                        (5,279,626)      (21,570,037)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Mining taxes</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>0.051214</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>0.057418</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>1.8e-05</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Diluted                                                                             357,492,812      312,915,843</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Equity $ (3,126,347) (5,337,044) 393,250 987,288 11,758 (126,614) 5,329,773 (1,867,936) 16,731,549 (21,621,251) 1,675,000</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>-3.126347</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>-0.014645</v>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>-  - -     11,758    13,800    151,509            -  -           103,000 -           $                        7,197,317                                                                                                                              7,374,384                                                  7,094,317                                                                                                                     7,197,317                                                    Surplus                                                                       Contributed</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>$                                                        Warrants</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Capital $ 46,186,602 - 331,053 796,125 - - 5,150,606 52,464,386 44,852,502 - 1,334,100</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>46.186602</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Share total</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Rémunération et paiements</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>fondés sur des actions                                                  -           582 000      Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.000853</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>0.000508</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Rémunération et paiements</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>fondés sur des actions                        582 000                            -      Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>6.7e-05</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.000552</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>prospection et d’évaluation                                             -           725 184      evaluation assets</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>prospection et d’évaluation                                             -           725 184      evaluation assets</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" s="5" t="n">
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" s="5" t="n">
         <v>0.000878</v>
       </c>
-      <c r="F117" s="5" t="n">
+      <c r="F141" s="5" t="n">
         <v>0.000223</v>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
